--- a/data/julio 2026/movimientos.xlsx
+++ b/data/julio 2026/movimientos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4879CD06-C3F9-47C0-B28E-3183A47875F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6673FF6-7E52-4F12-BF76-9D296470977E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="15375" windowHeight="7785" xr2:uid="{99072C7C-E32F-4A2F-800E-3105C8F1D176}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{99072C7C-E32F-4A2F-800E-3105C8F1D176}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>stockmov_fecha</t>
+  </si>
+  <si>
+    <t>articulo_codigo</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>stockmov_cantidad</t>
+  </si>
+  <si>
+    <t>bultos</t>
+  </si>
+  <si>
+    <t>unidades</t>
+  </si>
+  <si>
+    <t>stockmov_tipo</t>
+  </si>
+  <si>
+    <t>stockmov_motivo</t>
+  </si>
+  <si>
+    <t>deposito_id</t>
+  </si>
+  <si>
+    <t>deposito_nombre</t>
+  </si>
+  <si>
+    <t>uxb</t>
+  </si>
+  <si>
+    <t>costo</t>
+  </si>
+  <si>
+    <t>bultosAnt</t>
+  </si>
+  <si>
+    <t>unidadesAnt</t>
+  </si>
+  <si>
+    <t>bultosAct</t>
+  </si>
+  <si>
+    <t>unidadesAct</t>
+  </si>
+  <si>
+    <t>stockmov_comprobante</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -385,52 +437,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D248C6-4721-43B8-8122-45E55855FA17}">
-  <dimension ref="A2:A915"/>
+  <dimension ref="A1:Q915"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
